--- a/3-power-apps/power-apps-challenge/power-apps-challenge.xlsx
+++ b/3-power-apps/power-apps-challenge/power-apps-challenge.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/57d2ab2a84d54c81/Documents/GitHub/gxls-power-platform/3-power-apps/power-apps-challenge/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\gxls-power-platform\3-power-apps\power-apps-challenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{D3AE700D-647D-4501-B910-E6CA02E608F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78FD69F6-A3DF-4A6B-B6CB-2C21127F481A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21129600-BAC0-4F89-9F44-7CF2AC322F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -145,12 +145,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1426C0C4-7838-4D29-84E5-D70829F246BB}" name="Table1" displayName="Table1" ref="A1:E5" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1426C0C4-7838-4D29-84E5-D70829F246BB}" name="claims" displayName="claims" ref="A1:E5" totalsRowShown="0">
   <autoFilter ref="A1:E5" xr:uid="{1426C0C4-7838-4D29-84E5-D70829F246BB}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{55F8BFD6-C4FC-4C00-B089-DA9A0648BD4A}" name="Property ID"/>
@@ -452,7 +448,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" ht="129" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -469,7 +465,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:5" ht="129" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -486,7 +482,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" ht="143.35" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -503,7 +499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:5" ht="129" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>

--- a/3-power-apps/power-apps-challenge/power-apps-challenge.xlsx
+++ b/3-power-apps/power-apps-challenge/power-apps-challenge.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\gxls-power-platform\3-power-apps\power-apps-challenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21129600-BAC0-4F89-9F44-7CF2AC322F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5906218-34BE-4697-A224-D6DE8178A068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,12 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
-    <t>Property ID</t>
-  </si>
-  <si>
-    <t>Description of issue</t>
-  </si>
-  <si>
     <t>Date reported</t>
   </si>
   <si>
@@ -85,6 +79,12 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/stringfestdata/images-for-web-embeds/refs/heads/main/power-apps/Burst%20pipe.jpeg</t>
+  </si>
+  <si>
+    <t>PropertyID</t>
+  </si>
+  <si>
+    <t>DescriptionOfIssue</t>
   </si>
 </sst>
 </file>
@@ -149,8 +149,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1426C0C4-7838-4D29-84E5-D70829F246BB}" name="claims" displayName="claims" ref="A1:E5" totalsRowShown="0">
   <autoFilter ref="A1:E5" xr:uid="{1426C0C4-7838-4D29-84E5-D70829F246BB}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{55F8BFD6-C4FC-4C00-B089-DA9A0648BD4A}" name="Property ID"/>
-    <tableColumn id="2" xr3:uid="{F8DABAC4-7AD7-4CA1-A284-286C9E0846F9}" name="Description of issue"/>
+    <tableColumn id="1" xr3:uid="{55F8BFD6-C4FC-4C00-B089-DA9A0648BD4A}" name="PropertyID"/>
+    <tableColumn id="2" xr3:uid="{F8DABAC4-7AD7-4CA1-A284-286C9E0846F9}" name="DescriptionOfIssue"/>
     <tableColumn id="3" xr3:uid="{4B3F3E4E-27F9-4E22-BABA-49870B619933}" name="Date reported"/>
     <tableColumn id="4" xr3:uid="{E8864757-D816-4E54-B626-6D5CD61F85F3}" name="Status"/>
     <tableColumn id="5" xr3:uid="{C41BDAFA-328D-4180-B731-9DEF69BFBCE3}" name="LinkToImage"/>
@@ -433,87 +433,87 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="129" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2">
         <v>44936</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="129" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2">
         <v>44938</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="143.35" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2">
         <v>44941</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="129" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2">
         <v>44944</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
